--- a/web/public/forms/wih-hoeui.xlsx
+++ b/web/public/forms/wih-hoeui.xlsx
@@ -573,7 +573,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
         </is>
       </c>
       <c r="AK1" s="2" t="inlineStr">

--- a/web/public/forms/wih-hoeui.xlsx
+++ b/web/public/forms/wih-hoeui.xlsx
@@ -573,7 +573,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
         </is>
       </c>
       <c r="AK1" s="2" t="inlineStr">
